--- a/results/by_outcome/full_results_education_observed_Brothers_MI.xlsx
+++ b/results/by_outcome/full_results_education_observed_Brothers_MI.xlsx
@@ -486,10 +486,10 @@
         <v>#NUM!</v>
       </c>
       <c r="H2" t="n">
-        <v>0.532225852319976</v>
+        <v>0.54658763595125</v>
       </c>
       <c r="I2" t="n">
-        <v>0.245215098480355</v>
+        <v>0.241423623447595</v>
       </c>
       <c r="J2" t="e">
         <v>#NUM!</v>
@@ -507,7 +507,7 @@
         <v>#NUM!</v>
       </c>
       <c r="O2" t="n">
-        <v>0.468017138572981</v>
+        <v>0.453662250687476</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>#NUM!</v>
       </c>
       <c r="F3" t="n">
-        <v>0.534730000368156</v>
+        <v>0.543025957639057</v>
       </c>
       <c r="G3" t="n">
-        <v>0.253820808618324</v>
+        <v>0.253683610602672</v>
       </c>
       <c r="H3" t="e">
         <v>#NUM!</v>
@@ -565,13 +565,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.604931489434978</v>
+        <v>0.604494668942537</v>
       </c>
       <c r="D4" t="n">
-        <v>0.39552527286429</v>
+        <v>0.395962722566054</v>
       </c>
       <c r="E4" t="n">
-        <v>1.00045676229927</v>
+        <v>1.00045739150859</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -586,19 +586,19 @@
         <v>#NUM!</v>
       </c>
       <c r="J4" t="n">
-        <v>0.395344694061389</v>
+        <v>0.39578168967042</v>
       </c>
       <c r="K4" t="n">
-        <v>0.253704925388954</v>
+        <v>0.253567625304075</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0025030043383499</v>
+        <v>-0.00356004758565189</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0726724445115922</v>
+        <v>0.057880561017056</v>
       </c>
       <c r="N4" t="n">
-        <v>0.256207929727304</v>
+        <v>0.250007577718423</v>
       </c>
       <c r="O4" t="e">
         <v>#NUM!</v>
@@ -643,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.395344694061389</v>
+        <v>0.39578168967042</v>
       </c>
       <c r="D2" t="n">
-        <v>0.326016293277687</v>
+        <v>0.327520084361262</v>
       </c>
       <c r="E2" t="n">
-        <v>0.46467309484509</v>
+        <v>0.464043294979578</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0000000000000000000000000000530384602207649</v>
+        <v>0.00000000000000000000000000000635365160097741</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.256207929727304</v>
+        <v>0.250007577718423</v>
       </c>
       <c r="D3" t="n">
-        <v>0.185942182321547</v>
+        <v>0.186393518401614</v>
       </c>
       <c r="E3" t="n">
-        <v>0.326473677133061</v>
+        <v>0.313621637035232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00000000000104711206389144</v>
+        <v>0.0000000000000145068365414493</v>
       </c>
     </row>
     <row r="4">
@@ -683,16 +683,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.468017138572981</v>
+        <v>0.453662250687476</v>
       </c>
       <c r="D4" t="n">
-        <v>0.393333246754846</v>
+        <v>0.39181074789867</v>
       </c>
       <c r="E4" t="n">
-        <v>0.542701030391116</v>
+        <v>0.515513753476283</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000000000000000000000000000000000853525934003967</v>
+        <v>0.000000000000000000000000000000000000000000000224017280533355</v>
       </c>
     </row>
     <row r="5">
@@ -703,16 +703,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.211809208845677</v>
+        <v>0.203654672969053</v>
       </c>
       <c r="D5" t="n">
-        <v>0.172532998790099</v>
+        <v>0.164144186430637</v>
       </c>
       <c r="E5" t="n">
-        <v>0.251085418901255</v>
+        <v>0.24316515950747</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000000000000000000000013698588809404</v>
+        <v>0.000000000000000000000105019983024418</v>
       </c>
     </row>
   </sheetData>
